--- a/exports/trend_1d/DABUR_full_report.xlsx
+++ b/exports/trend_1d/DABUR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.75</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42121</v>
+        <v>42122</v>
       </c>
       <c r="H2" t="n">
-        <v>263.45</v>
+        <v>259.1</v>
       </c>
       <c r="I2" t="n">
         <v>261.731741241932</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K2" t="n">
-        <v>5.42</v>
+        <v>3.68</v>
       </c>
       <c r="L2" t="n">
         <v>1.86</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42178</v>
+        <v>42179</v>
       </c>
       <c r="H3" t="n">
-        <v>269.75</v>
+        <v>273.5</v>
       </c>
       <c r="I3" t="n">
         <v>272.3100702520461</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.11</v>
+        <v>-5.56</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>298.64</v>
+        <v>273.45</v>
       </c>
       <c r="I4" t="n">
         <v>286.5671849276874</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K4" t="n">
-        <v>9.19</v>
+        <v>-0.02</v>
       </c>
       <c r="L4" t="n">
         <v>4.94</v>
       </c>
       <c r="M4" t="n">
-        <v>0.93</v>
+        <v>2.89</v>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>8.43</v>
       </c>
       <c r="O4" t="n">
         <v>1.39</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42339</v>
+        <v>42340</v>
       </c>
       <c r="H5" t="n">
-        <v>278.5</v>
+        <v>283.89</v>
       </c>
       <c r="I5" t="n">
         <v>280.3852494669289</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.85</v>
+        <v>-3.82</v>
       </c>
       <c r="L5" t="n">
         <v>7.37</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.32</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42377</v>
+        <v>42380</v>
       </c>
       <c r="H6" t="n">
-        <v>269.05</v>
+        <v>263.1</v>
       </c>
       <c r="I6" t="n">
         <v>263.6418361900853</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.23</v>
+        <v>-7.32</v>
       </c>
       <c r="L6" t="n">
-        <v>7.75</v>
+        <v>7.83</v>
       </c>
       <c r="M6" t="n">
         <v>2.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42471</v>
+        <v>42472</v>
       </c>
       <c r="H7" t="n">
-        <v>253.4</v>
+        <v>262.8</v>
       </c>
       <c r="I7" t="n">
         <v>256.078443570106</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K7" t="n">
-        <v>3.69</v>
+        <v>0.11</v>
       </c>
       <c r="L7" t="n">
         <v>1.69</v>
@@ -840,7 +923,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>-2.21</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42585</v>
+        <v>42586</v>
       </c>
       <c r="H8" t="n">
-        <v>296.95</v>
+        <v>295.65</v>
       </c>
       <c r="I8" t="n">
         <v>296.4622801374569</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K8" t="n">
-        <v>12.99</v>
+        <v>12.5</v>
       </c>
       <c r="L8" t="n">
         <v>3.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.38</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H9" t="n">
-        <v>285.1</v>
+        <v>296.7</v>
       </c>
       <c r="I9" t="n">
         <v>287.1373140563383</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>3.57</v>
+        <v>-0.36</v>
       </c>
       <c r="L9" t="n">
         <v>3.48</v>
@@ -954,7 +1061,7 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.97</v>
+        <v>4.07</v>
       </c>
       <c r="O9" t="n">
         <v>-0.44</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H10" t="n">
-        <v>280.45</v>
+        <v>270.75</v>
       </c>
       <c r="I10" t="n">
         <v>278.5802839995293</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.48</v>
+        <v>-8.75</v>
       </c>
       <c r="L10" t="n">
-        <v>8.17</v>
+        <v>9.17</v>
       </c>
       <c r="M10" t="n">
         <v>4.28</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.45</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H11" t="n">
-        <v>276.55</v>
+        <v>278.85</v>
       </c>
       <c r="I11" t="n">
         <v>278.6989579242806</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.14</v>
+        <v>-2.99</v>
       </c>
       <c r="L11" t="n">
         <v>6.48</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42774</v>
+        <v>42775</v>
       </c>
       <c r="H12" t="n">
-        <v>265.95</v>
+        <v>265.75</v>
       </c>
       <c r="I12" t="n">
         <v>265.9393936166864</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.63</v>
+        <v>-4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>5.18</v>
+        <v>5.29</v>
       </c>
       <c r="M12" t="n">
         <v>0.24</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42811</v>
+        <v>42814</v>
       </c>
       <c r="H13" t="n">
-        <v>278.1</v>
+        <v>278.9</v>
       </c>
       <c r="I13" t="n">
         <v>278.173277278082</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.65</v>
+        <v>-4.95</v>
       </c>
       <c r="L13" t="n">
-        <v>5.74</v>
+        <v>6.49</v>
       </c>
       <c r="M13" t="n">
         <v>0.77</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.75</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H14" t="n">
-        <v>284.9</v>
+        <v>275.75</v>
       </c>
       <c r="I14" t="n">
         <v>280.2879483259126</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K14" t="n">
-        <v>2.15</v>
+        <v>-1.13</v>
       </c>
       <c r="L14" t="n">
         <v>2.37</v>
@@ -1239,7 +1406,7 @@
         <v>0.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.42</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
         <v>0.29</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42886</v>
+        <v>42887</v>
       </c>
       <c r="H15" t="n">
-        <v>279.95</v>
+        <v>285.35</v>
       </c>
       <c r="I15" t="n">
         <v>285.113140706424</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.52</v>
+        <v>-3.48</v>
       </c>
       <c r="L15" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="M15" t="n">
         <v>1.29</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.79</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43133</v>
+        <v>43136</v>
       </c>
       <c r="H16" t="n">
-        <v>344.45</v>
+        <v>339.1</v>
       </c>
       <c r="I16" t="n">
         <v>343.8176435065472</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K16" t="n">
-        <v>20.71</v>
+        <v>18.84</v>
       </c>
       <c r="L16" t="n">
         <v>2.75</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H17" t="n">
-        <v>336.9</v>
+        <v>342.85</v>
       </c>
       <c r="I17" t="n">
         <v>338.6121147026106</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" t="n">
-        <v>0.65</v>
+        <v>-1.11</v>
       </c>
       <c r="L17" t="n">
         <v>2.92</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H18" t="n">
-        <v>376.1</v>
+        <v>367.3</v>
       </c>
       <c r="I18" t="n">
         <v>369.7419340160874</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K18" t="n">
-        <v>9.699999999999999</v>
+        <v>7.13</v>
       </c>
       <c r="L18" t="n">
         <v>2.14</v>
@@ -1467,7 +1682,7 @@
         <v>0.71</v>
       </c>
       <c r="N18" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
         <v>1.77</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.23</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="H19" t="n">
-        <v>393.45</v>
+        <v>421.55</v>
       </c>
       <c r="I19" t="n">
         <v>393.8600894202871</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.12</v>
+        <v>-14.77</v>
       </c>
       <c r="L19" t="n">
-        <v>7.79</v>
+        <v>16.65</v>
       </c>
       <c r="M19" t="n">
         <v>1.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>7.14</v>
       </c>
       <c r="O19" t="n">
         <v>-2.34</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.89</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H20" t="n">
-        <v>466.35</v>
+        <v>448.6</v>
       </c>
       <c r="I20" t="n">
         <v>449.4941271151084</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>10.63</v>
+        <v>6.42</v>
       </c>
       <c r="L20" t="n">
         <v>8.75</v>
@@ -1581,7 +1820,7 @@
         <v>1.61</v>
       </c>
       <c r="N20" t="n">
-        <v>2.59</v>
+        <v>3.81</v>
       </c>
       <c r="O20" t="n">
         <v>7.14</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.32</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43426</v>
+        <v>43430</v>
       </c>
       <c r="H21" t="n">
-        <v>400.8</v>
+        <v>419.05</v>
       </c>
       <c r="I21" t="n">
         <v>409.5149060110821</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K21" t="n">
-        <v>10.66</v>
+        <v>6.59</v>
       </c>
       <c r="L21" t="n">
         <v>5.92</v>
@@ -1638,7 +1889,7 @@
         <v>1.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.69</v>
+        <v>4.55</v>
       </c>
       <c r="O21" t="n">
         <v>-3.81</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43511</v>
+        <v>43514</v>
       </c>
       <c r="H22" t="n">
-        <v>434.3</v>
+        <v>422.35</v>
       </c>
       <c r="I22" t="n">
         <v>425.300419876107</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K22" t="n">
-        <v>3.64</v>
+        <v>0.79</v>
       </c>
       <c r="L22" t="n">
         <v>5.74</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H23" t="n">
-        <v>385.45</v>
+        <v>399.05</v>
       </c>
       <c r="I23" t="n">
         <v>385.7099406979819</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" t="n">
-        <v>8.74</v>
+        <v>5.52</v>
       </c>
       <c r="L23" t="n">
         <v>7.66</v>
@@ -1752,7 +2027,7 @@
         <v>2.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.34</v>
+        <v>3.53</v>
       </c>
       <c r="O23" t="n">
         <v>-2.75</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H24" t="n">
-        <v>387.7</v>
+        <v>381.95</v>
       </c>
       <c r="I24" t="n">
         <v>383.636534583006</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.84</v>
+        <v>-4.29</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
         <v>0.71</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H25" t="n">
-        <v>407.7</v>
+        <v>410.7</v>
       </c>
       <c r="I25" t="n">
         <v>410.5150146600898</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.74</v>
+        <v>-7.53</v>
       </c>
       <c r="L25" t="n">
         <v>8.130000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>6.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H26" t="n">
-        <v>439.65</v>
+        <v>433.65</v>
       </c>
       <c r="I26" t="n">
         <v>433.9861229476331</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>7.05</v>
+        <v>5.59</v>
       </c>
       <c r="L26" t="n">
         <v>1.11</v>
       </c>
       <c r="M26" t="n">
-        <v>0.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>2.8</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43754</v>
+        <v>43755</v>
       </c>
       <c r="H27" t="n">
-        <v>456.1</v>
+        <v>462.4</v>
       </c>
       <c r="I27" t="n">
         <v>460.3603093807095</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.18</v>
+        <v>-6.63</v>
       </c>
       <c r="L27" t="n">
-        <v>5.86</v>
+        <v>6.91</v>
       </c>
       <c r="M27" t="n">
         <v>0.79</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H28" t="n">
-        <v>488</v>
+        <v>455.25</v>
       </c>
       <c r="I28" t="n">
         <v>481.7859204140632</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K28" t="n">
-        <v>5.54</v>
+        <v>-1.55</v>
       </c>
       <c r="L28" t="n">
         <v>3.61</v>
       </c>
       <c r="M28" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="N28" t="n">
-        <v>3.48</v>
+        <v>6.71</v>
       </c>
       <c r="O28" t="n">
         <v>1.38</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>13.28</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H29" t="n">
-        <v>477.55</v>
+        <v>488.3</v>
       </c>
       <c r="I29" t="n">
         <v>484.3508067265935</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.9</v>
+        <v>-7.26</v>
       </c>
       <c r="L29" t="n">
-        <v>7.41</v>
+        <v>13.65</v>
       </c>
       <c r="M29" t="n">
         <v>4.45</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>19.46</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H30" t="n">
-        <v>433.1</v>
+        <v>428.95</v>
       </c>
       <c r="I30" t="n">
         <v>431.0098524646282</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.3</v>
+        <v>-12.15</v>
       </c>
       <c r="L30" t="n">
-        <v>12.47</v>
+        <v>13.15</v>
       </c>
       <c r="M30" t="n">
         <v>1.9</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.44</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44018</v>
+        <v>44019</v>
       </c>
       <c r="H31" t="n">
-        <v>465.95</v>
+        <v>478.55</v>
       </c>
       <c r="I31" t="n">
         <v>473.7183209014896</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.630000000000001</v>
+        <v>-11.56</v>
       </c>
       <c r="L31" t="n">
-        <v>11.18</v>
+        <v>12.34</v>
       </c>
       <c r="M31" t="n">
         <v>1.44</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.18</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H32" t="n">
-        <v>489.1</v>
+        <v>474.6</v>
       </c>
       <c r="I32" t="n">
         <v>478.1047589142004</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K32" t="n">
-        <v>2.2</v>
+        <v>-0.83</v>
       </c>
       <c r="L32" t="n">
         <v>3.26</v>
@@ -2265,7 +2648,7 @@
         <v>1.53</v>
       </c>
       <c r="N32" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
         <v>2.7</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.24</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H33" t="n">
-        <v>513.8</v>
+        <v>520</v>
       </c>
       <c r="I33" t="n">
         <v>518.4387130018889</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.26</v>
+        <v>-9.57</v>
       </c>
       <c r="L33" t="n">
-        <v>9.02</v>
+        <v>9.91</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.91</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H34" t="n">
-        <v>527.9</v>
+        <v>514.55</v>
       </c>
       <c r="I34" t="n">
         <v>515.5516657538813</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K34" t="n">
-        <v>1.52</v>
+        <v>-1.05</v>
       </c>
       <c r="L34" t="n">
         <v>5.28</v>
@@ -2379,7 +2786,7 @@
         <v>0.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="O34" t="n">
         <v>1.21</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44281</v>
+        <v>44285</v>
       </c>
       <c r="H35" t="n">
-        <v>529.8</v>
+        <v>538</v>
       </c>
       <c r="I35" t="n">
         <v>536.1100890765133</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.96</v>
+        <v>-4.56</v>
       </c>
       <c r="L35" t="n">
         <v>5.81</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.99</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="H36" t="n">
-        <v>559.95</v>
+        <v>541.3</v>
       </c>
       <c r="I36" t="n">
         <v>543.4366838939535</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K36" t="n">
-        <v>4.08</v>
+        <v>0.61</v>
       </c>
       <c r="L36" t="n">
         <v>1.12</v>
@@ -2493,7 +2924,7 @@
         <v>1.74</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>3.33</v>
       </c>
       <c r="O36" t="n">
         <v>1.55</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.5</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44354</v>
+        <v>44355</v>
       </c>
       <c r="H37" t="n">
-        <v>548.5</v>
+        <v>556.35</v>
       </c>
       <c r="I37" t="n">
         <v>554.4680534857938</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.33</v>
+        <v>-2.78</v>
       </c>
       <c r="L37" t="n">
         <v>3.93</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.88</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44468</v>
+        <v>44469</v>
       </c>
       <c r="H38" t="n">
-        <v>623.15</v>
+        <v>617.05</v>
       </c>
       <c r="I38" t="n">
         <v>621.287771574178</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K38" t="n">
-        <v>12.01</v>
+        <v>10.91</v>
       </c>
       <c r="L38" t="n">
         <v>0.8100000000000001</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.38</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H39" t="n">
-        <v>582.55</v>
+        <v>587.5</v>
       </c>
       <c r="I39" t="n">
         <v>587.1667810094597</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K39" t="n">
-        <v>5.59</v>
+        <v>4.79</v>
       </c>
       <c r="L39" t="n">
         <v>2.42</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.82</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H40" t="n">
-        <v>568.55</v>
+        <v>559.85</v>
       </c>
       <c r="I40" t="n">
         <v>562.3375470050812</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.23</v>
+        <v>-4.71</v>
       </c>
       <c r="L40" t="n">
-        <v>4.68</v>
+        <v>5.32</v>
       </c>
       <c r="M40" t="n">
         <v>0.71</v>
       </c>
       <c r="N40" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="O40" t="n">
         <v>0.85</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.56</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44595</v>
+        <v>44596</v>
       </c>
       <c r="H41" t="n">
-        <v>556.45</v>
+        <v>569</v>
       </c>
       <c r="I41" t="n">
         <v>566.2834364758106</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>0.61</v>
+        <v>-1.63</v>
       </c>
       <c r="L41" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
         <v>0.82</v>
       </c>
       <c r="N41" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="O41" t="n">
         <v>-1.53</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.21</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H42" t="n">
-        <v>543.25</v>
+        <v>533.7</v>
       </c>
       <c r="I42" t="n">
         <v>533.815233309816</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.53</v>
+        <v>-6.2</v>
       </c>
       <c r="L42" t="n">
-        <v>4.99</v>
+        <v>7.49</v>
       </c>
       <c r="M42" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="N42" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="O42" t="n">
         <v>2.26</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.59</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H43" t="n">
-        <v>555.9</v>
+        <v>562.7</v>
       </c>
       <c r="I43" t="n">
         <v>560.8639105899817</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.16</v>
+        <v>-5.43</v>
       </c>
       <c r="L43" t="n">
         <v>6.94</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44685</v>
+        <v>44686</v>
       </c>
       <c r="H44" t="n">
-        <v>538.05</v>
+        <v>529.05</v>
       </c>
       <c r="I44" t="n">
         <v>529.7879020492035</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.38</v>
+        <v>-5.98</v>
       </c>
       <c r="L44" t="n">
-        <v>5.4</v>
+        <v>6.95</v>
       </c>
       <c r="M44" t="n">
         <v>1.06</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.77</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H45" t="n">
-        <v>511.25</v>
+        <v>525</v>
       </c>
       <c r="I45" t="n">
         <v>523.9398814547751</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K45" t="n">
-        <v>3.36</v>
+        <v>0.77</v>
       </c>
       <c r="L45" t="n">
         <v>2.72</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.44</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H46" t="n">
-        <v>563.45</v>
+        <v>546.4</v>
       </c>
       <c r="I46" t="n">
         <v>558.9394520113572</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K46" t="n">
-        <v>7.32</v>
+        <v>4.08</v>
       </c>
       <c r="L46" t="n">
         <v>2.62</v>
@@ -3063,7 +3614,7 @@
         <v>3.18</v>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="O46" t="n">
         <v>2.69</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.83</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H47" t="n">
-        <v>554.7</v>
+        <v>563.8</v>
       </c>
       <c r="I47" t="n">
         <v>563.6738475823029</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.52</v>
+        <v>-3.18</v>
       </c>
       <c r="L47" t="n">
         <v>6.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.41</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>577.75</v>
+        <v>565.85</v>
       </c>
       <c r="I48" t="n">
         <v>566.6454168166647</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K48" t="n">
-        <v>2.47</v>
+        <v>0.36</v>
       </c>
       <c r="L48" t="n">
         <v>4.12</v>
@@ -3177,7 +3752,7 @@
         <v>2.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="O48" t="n">
         <v>1.64</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.29</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="H49" t="n">
-        <v>530.15</v>
+        <v>542.1</v>
       </c>
       <c r="I49" t="n">
         <v>540.1160972864399</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K49" t="n">
-        <v>6.31</v>
+        <v>4.2</v>
       </c>
       <c r="L49" t="n">
         <v>2.02</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>7</v>
+      </c>
+      <c r="U49" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.28</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H50" t="n">
-        <v>565.65</v>
+        <v>555.05</v>
       </c>
       <c r="I50" t="n">
         <v>561.6565475530434</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K50" t="n">
-        <v>4.34</v>
+        <v>2.39</v>
       </c>
       <c r="L50" t="n">
         <v>2.51</v>
       </c>
       <c r="M50" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="N50" t="n">
         <v>3.34</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.68</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H51" t="n">
-        <v>535.5</v>
+        <v>537.95</v>
       </c>
       <c r="I51" t="n">
         <v>536.6992248555196</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K51" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="L51" t="n">
         <v>6.97</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45280</v>
+        <v>45281</v>
       </c>
       <c r="H52" t="n">
-        <v>534.95</v>
+        <v>530.25</v>
       </c>
       <c r="I52" t="n">
         <v>530.8902999654561</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.43</v>
       </c>
       <c r="L52" t="n">
         <v>3.95</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45288</v>
+        <v>45289</v>
       </c>
       <c r="H53" t="n">
-        <v>543.1</v>
+        <v>557.2</v>
       </c>
       <c r="I53" t="n">
         <v>555.4985515899454</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.42</v>
+        <v>-5.08</v>
       </c>
       <c r="L53" t="n">
-        <v>2.92</v>
+        <v>5.61</v>
       </c>
       <c r="M53" t="n">
         <v>0.32</v>
       </c>
       <c r="N53" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
         <v>-0.88</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.97</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H54" t="n">
-        <v>538.4</v>
+        <v>524.8</v>
       </c>
       <c r="I54" t="n">
         <v>537.1447850810067</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.37</v>
+        <v>-5.81</v>
       </c>
       <c r="L54" t="n">
-        <v>3.92</v>
+        <v>6.21</v>
       </c>
       <c r="M54" t="n">
         <v>0.59</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.07</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H55" t="n">
-        <v>507.75</v>
+        <v>525.3</v>
       </c>
       <c r="I55" t="n">
         <v>519.6092332578764</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>3.25</v>
+        <v>-0.1</v>
       </c>
       <c r="L55" t="n">
         <v>9.66</v>
@@ -3576,7 +4235,7 @@
         <v>1.37</v>
       </c>
       <c r="N55" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="O55" t="n">
         <v>-2.53</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.05</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="H56" t="n">
-        <v>655.85</v>
+        <v>627</v>
       </c>
       <c r="I56" t="n">
         <v>629.8918159683097</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K56" t="n">
-        <v>24.85</v>
+        <v>19.36</v>
       </c>
       <c r="L56" t="n">
         <v>3.29</v>
@@ -3633,7 +4304,7 @@
         <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="O56" t="n">
         <v>3.46</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.75</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="H57" t="n">
-        <v>518.1</v>
+        <v>533.7</v>
       </c>
       <c r="I57" t="n">
         <v>528.90186285494</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K57" t="n">
-        <v>17.37</v>
+        <v>14.88</v>
       </c>
       <c r="L57" t="n">
         <v>4.3</v>
@@ -3690,7 +4373,7 @@
         <v>0.79</v>
       </c>
       <c r="N57" t="n">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="O57" t="n">
         <v>-4.4</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.2</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H58" t="n">
-        <v>503.25</v>
+        <v>493.3</v>
       </c>
       <c r="I58" t="n">
         <v>498.0491086334898</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.71</v>
+        <v>-7.57</v>
       </c>
       <c r="L58" t="n">
-        <v>6.29</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M58" t="n">
         <v>0.99</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="H59" t="n">
-        <v>486.2</v>
+        <v>491.7</v>
       </c>
       <c r="I59" t="n">
         <v>486.6903719712538</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K59" t="n">
-        <v>1.44</v>
+        <v>0.32</v>
       </c>
       <c r="L59" t="n">
         <v>5.3</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H60" t="n">
-        <v>472.95</v>
+        <v>466.5</v>
       </c>
       <c r="I60" t="n">
         <v>467.5375963790958</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.81</v>
+        <v>-5.13</v>
       </c>
       <c r="L60" t="n">
         <v>6.73</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>5.55</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H61" t="n">
-        <v>482.4</v>
+        <v>487.55</v>
       </c>
       <c r="I61" t="n">
         <v>487.4992154923884</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.41</v>
+        <v>-4.51</v>
       </c>
       <c r="L61" t="n">
         <v>4.87</v>
       </c>
       <c r="M61" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="N61" t="n">
         <v>1.63</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.3</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H62" t="n">
-        <v>517.2</v>
+        <v>507.25</v>
       </c>
       <c r="I62" t="n">
         <v>509.329657989735</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K62" t="n">
-        <v>6.08</v>
+        <v>4.04</v>
       </c>
       <c r="L62" t="n">
         <v>1.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.28</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H63" t="n">
-        <v>522.05</v>
+        <v>535</v>
       </c>
       <c r="I63" t="n">
         <v>531.5258944030641</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.92</v>
+        <v>-5.47</v>
       </c>
       <c r="L63" t="n">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="M63" t="n">
         <v>2.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.74</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H64" t="n">
-        <v>522.05</v>
+        <v>515</v>
       </c>
       <c r="I64" t="n">
         <v>520.8600821754993</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.42</v>
+        <v>-3.74</v>
       </c>
       <c r="L64" t="n">
         <v>4.73</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H65" t="n">
-        <v>503.3</v>
+        <v>517.05</v>
       </c>
       <c r="I65" t="n">
         <v>515.1208232980364</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>2.27</v>
+        <v>-0.4</v>
       </c>
       <c r="L65" t="n">
         <v>1.36</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.79</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H66" t="n">
-        <v>501.75</v>
+        <v>495</v>
       </c>
       <c r="I66" t="n">
         <v>495.7067750667393</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.96</v>
+        <v>-4.26</v>
       </c>
       <c r="L66" t="n">
-        <v>3.95</v>
+        <v>4.46</v>
       </c>
       <c r="M66" t="n">
         <v>0.95</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.89</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H67" t="n">
-        <v>499.95</v>
+        <v>522.6</v>
       </c>
       <c r="I67" t="n">
         <v>507.965706113844</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-1</v>
+        <v>-5.58</v>
       </c>
       <c r="L67" t="n">
-        <v>3.01</v>
+        <v>6.33</v>
       </c>
       <c r="M67" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="N67" t="n">
-        <v>1.6</v>
+        <v>4.53</v>
       </c>
       <c r="O67" t="n">
         <v>-1.35</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.45</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H68" t="n">
-        <v>507.6</v>
+        <v>487.4</v>
       </c>
       <c r="I68" t="n">
         <v>496.6264036968363</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.87</v>
+        <v>-6.74</v>
       </c>
       <c r="L68" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
         <v>3.41</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>3.98</v>
       </c>
       <c r="O68" t="n">
         <v>4.53</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H69" t="n">
-        <v>441.7</v>
+        <v>452</v>
       </c>
       <c r="I69" t="n">
         <v>449.96232069793</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K69" t="n">
-        <v>9.380000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="L69" t="n">
         <v>3.6</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.12</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H70" t="n">
-        <v>443.4</v>
+        <v>424.6</v>
       </c>
       <c r="I70" t="n">
         <v>440.8569316343347</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.9</v>
+        <v>-6.06</v>
       </c>
       <c r="L70" t="n">
-        <v>2.87</v>
+        <v>6.31</v>
       </c>
       <c r="M70" t="n">
         <v>1.53</v>
       </c>
       <c r="N70" t="n">
-        <v>3.18</v>
+        <v>4.24</v>
       </c>
       <c r="O70" t="n">
         <v>2.33</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>10.25</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="H71" t="n">
-        <v>444.75</v>
+        <v>447</v>
       </c>
       <c r="I71" t="n">
         <v>446.4452291744788</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.75</v>
+        <v>-5.28</v>
       </c>
       <c r="L71" t="n">
-        <v>5.28</v>
+        <v>6.22</v>
       </c>
       <c r="M71" t="n">
         <v>1.43</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.44</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="H72" t="n">
-        <v>426.1</v>
+        <v>421.45</v>
       </c>
       <c r="I72" t="n">
         <v>422.4846809164515</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.68</v>
+        <v>-5.72</v>
       </c>
       <c r="L72" t="n">
         <v>7.04</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.58</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H73" t="n">
-        <v>384.55</v>
+        <v>395.25</v>
       </c>
       <c r="I73" t="n">
         <v>389.451138549467</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K73" t="n">
-        <v>8.76</v>
+        <v>6.22</v>
       </c>
       <c r="L73" t="n">
         <v>1.97</v>
@@ -4602,7 +5477,7 @@
         <v>0.8</v>
       </c>
       <c r="N73" t="n">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="O73" t="n">
         <v>-1.09</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.19</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="H74" t="n">
-        <v>379.05</v>
+        <v>368</v>
       </c>
       <c r="I74" t="n">
         <v>369.4004096596837</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.1</v>
+        <v>-6.89</v>
       </c>
       <c r="L74" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
         <v>1.33</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>5</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.3</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110.8</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="11">
@@ -9737,7 +10644,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9747,7 +10654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -9757,7 +10664,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.11</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.27</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.85</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.9</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.81</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.68</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.47</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="25">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="27">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
